--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_1_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_1_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A61E42-CB88-45DF-94E2-34346BC39F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659B55B1-753E-41B2-873D-5D100539FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,10 +55,58 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT IGL 24 Apr 2025 170 PE</t>
-  </si>
-  <si>
-    <t>09-04-2025</t>
+    <t>OPT ITC 29 May 2025 430 CE</t>
+  </si>
+  <si>
+    <t>12-05-2025</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 15 May 2025 24500 CE</t>
+  </si>
+  <si>
+    <t>OPT BEL 29 May 2025 330 CE</t>
+  </si>
+  <si>
+    <t>13-05-2025</t>
+  </si>
+  <si>
+    <t>OPT DRREDDY 29 May 2025 1200 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 15 May 2025 24700 PE</t>
+  </si>
+  <si>
+    <t>OPT TATASTEEL 29 May 2025 150 CE</t>
+  </si>
+  <si>
+    <t>14-05-2025</t>
+  </si>
+  <si>
+    <t>OPT TITAGARH 29 May 2025 800 CE</t>
+  </si>
+  <si>
+    <t>15-05-2025</t>
+  </si>
+  <si>
+    <t>OPT TATAMOTORS 29 May 2025 720 CE</t>
+  </si>
+  <si>
+    <t>16-05-2025</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 29 May 2025 1000 CE</t>
+  </si>
+  <si>
+    <t>OPT ATGL 29 May 2025 670 CE</t>
+  </si>
+  <si>
+    <t>OPT TITAGARH 29 May 2025 820 CE</t>
+  </si>
+  <si>
+    <t>OPT ATGL 29 May 2025 660 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 22 May 2025 25000 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -411,13 +459,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -431,10 +478,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -443,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -469,49 +516,613 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45756</v>
+        <v>45789</v>
       </c>
       <c r="D2">
-        <v>2750</v>
+        <v>1600</v>
       </c>
       <c r="E2">
-        <v>6.3</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="F2">
-        <v>17325</v>
+        <v>16320</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>2750</v>
+        <v>1600</v>
       </c>
       <c r="I2">
-        <v>6.75</v>
+        <v>10.75</v>
       </c>
       <c r="J2">
-        <v>18562.5</v>
+        <v>17200</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1237.5</v>
+        <v>880</v>
       </c>
       <c r="M2">
-        <v>82.29</v>
+        <v>78.98</v>
       </c>
       <c r="N2">
-        <v>1155.21</v>
+        <v>801.02</v>
       </c>
       <c r="O2">
-        <v>1237.5</v>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45789</v>
+      </c>
+      <c r="D3">
+        <v>75</v>
+      </c>
+      <c r="E3">
+        <v>302.85000000000002</v>
+      </c>
+      <c r="F3">
+        <v>22713.75</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>318.10000000000002</v>
+      </c>
+      <c r="J3">
+        <v>23857.5</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1143.75</v>
+      </c>
+      <c r="M3">
+        <v>91.09</v>
+      </c>
+      <c r="N3">
+        <v>1052.6600000000001</v>
+      </c>
+      <c r="O3">
+        <v>1143.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45790</v>
+      </c>
+      <c r="D4">
+        <v>2850</v>
+      </c>
+      <c r="E4">
+        <v>10.6</v>
+      </c>
+      <c r="F4">
+        <v>30210</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>2850</v>
+      </c>
+      <c r="I4">
+        <v>10.7</v>
+      </c>
+      <c r="J4">
+        <v>30495</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>285</v>
+      </c>
+      <c r="M4">
+        <v>103.73</v>
+      </c>
+      <c r="N4">
+        <v>181.27</v>
+      </c>
+      <c r="O4">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45790</v>
+      </c>
+      <c r="D5">
+        <v>625</v>
+      </c>
+      <c r="E5">
+        <v>44.5</v>
+      </c>
+      <c r="F5">
+        <v>27812.5</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>625</v>
+      </c>
+      <c r="I5">
+        <v>46.55</v>
+      </c>
+      <c r="J5">
+        <v>29093.75</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1281.25</v>
+      </c>
+      <c r="M5">
+        <v>101.05</v>
+      </c>
+      <c r="N5">
+        <v>1180.2</v>
+      </c>
+      <c r="O5">
+        <v>1281.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>192</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45790</v>
+      </c>
+      <c r="D6">
+        <v>375</v>
+      </c>
+      <c r="E6">
+        <v>194.02</v>
+      </c>
+      <c r="F6">
+        <v>72757.5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>375</v>
+      </c>
+      <c r="I6">
+        <v>197</v>
+      </c>
+      <c r="J6">
+        <v>73875</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1117.5</v>
+      </c>
+      <c r="M6">
+        <v>350.11</v>
+      </c>
+      <c r="N6">
+        <v>767.39</v>
+      </c>
+      <c r="O6">
+        <v>1117.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>271</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45791</v>
+      </c>
+      <c r="D7">
+        <v>11000</v>
+      </c>
+      <c r="E7">
+        <v>7.53</v>
+      </c>
+      <c r="F7">
+        <v>82775</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>11000</v>
+      </c>
+      <c r="I7">
+        <v>7.75</v>
+      </c>
+      <c r="J7">
+        <v>85250</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>2475</v>
+      </c>
+      <c r="M7">
+        <v>252.05</v>
+      </c>
+      <c r="N7">
+        <v>2222.9499999999998</v>
+      </c>
+      <c r="O7">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>278</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45792</v>
+      </c>
+      <c r="D8">
+        <v>625</v>
+      </c>
+      <c r="E8">
+        <v>42.5</v>
+      </c>
+      <c r="F8">
+        <v>26562.5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8">
+        <v>625</v>
+      </c>
+      <c r="I8">
+        <v>45.95</v>
+      </c>
+      <c r="J8">
+        <v>28718.75</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>2156.25</v>
+      </c>
+      <c r="M8">
+        <v>100.18</v>
+      </c>
+      <c r="N8">
+        <v>2056.0700000000002</v>
+      </c>
+      <c r="O8">
+        <v>2156.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>270</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45792</v>
+      </c>
+      <c r="D9">
+        <v>550</v>
+      </c>
+      <c r="E9">
+        <v>22.45</v>
+      </c>
+      <c r="F9">
+        <v>12347.5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>550</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>16500</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>4152.5</v>
+      </c>
+      <c r="M9">
+        <v>76.2</v>
+      </c>
+      <c r="N9">
+        <v>4076.3</v>
+      </c>
+      <c r="O9">
+        <v>4152.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45792</v>
+      </c>
+      <c r="D10">
+        <v>675</v>
+      </c>
+      <c r="E10">
+        <v>33.4</v>
+      </c>
+      <c r="F10">
+        <v>22545</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10">
+        <v>675</v>
+      </c>
+      <c r="I10">
+        <v>35.85</v>
+      </c>
+      <c r="J10">
+        <v>24198.75</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1653.75</v>
+      </c>
+      <c r="M10">
+        <v>91.73</v>
+      </c>
+      <c r="N10">
+        <v>1562.02</v>
+      </c>
+      <c r="O10">
+        <v>1653.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45793</v>
+      </c>
+      <c r="D11">
+        <v>775</v>
+      </c>
+      <c r="E11">
+        <v>22.25</v>
+      </c>
+      <c r="F11">
+        <v>17243.75</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11">
+        <v>775</v>
+      </c>
+      <c r="I11">
+        <v>22.5</v>
+      </c>
+      <c r="J11">
+        <v>17437.5</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>193.75</v>
+      </c>
+      <c r="M11">
+        <v>79.739999999999995</v>
+      </c>
+      <c r="N11">
+        <v>114.01</v>
+      </c>
+      <c r="O11">
+        <v>193.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>279</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45793</v>
+      </c>
+      <c r="D12">
+        <v>625</v>
+      </c>
+      <c r="E12">
+        <v>73</v>
+      </c>
+      <c r="F12">
+        <v>45625</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12">
+        <v>625</v>
+      </c>
+      <c r="I12">
+        <v>72.25</v>
+      </c>
+      <c r="J12">
+        <v>45156.25</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>-468.75</v>
+      </c>
+      <c r="M12">
+        <v>132.35</v>
+      </c>
+      <c r="N12">
+        <v>-601.1</v>
+      </c>
+      <c r="O12">
+        <v>468.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45793</v>
+      </c>
+      <c r="D13">
+        <v>775</v>
+      </c>
+      <c r="E13">
+        <v>28.15</v>
+      </c>
+      <c r="F13">
+        <v>21816.25</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13">
+        <v>775</v>
+      </c>
+      <c r="I13">
+        <v>29</v>
+      </c>
+      <c r="J13">
+        <v>22475</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>658.75</v>
+      </c>
+      <c r="M13">
+        <v>88.95</v>
+      </c>
+      <c r="N13">
+        <v>569.79999999999995</v>
+      </c>
+      <c r="O13">
+        <v>658.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>202</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45793</v>
+      </c>
+      <c r="D14">
+        <v>75</v>
+      </c>
+      <c r="E14">
+        <v>196.2</v>
+      </c>
+      <c r="F14">
+        <v>14715</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14">
+        <v>75</v>
+      </c>
+      <c r="I14">
+        <v>186.2</v>
+      </c>
+      <c r="J14">
+        <v>13965</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>-750</v>
+      </c>
+      <c r="M14">
+        <v>73.67</v>
+      </c>
+      <c r="N14">
+        <v>-823.67</v>
+      </c>
+      <c r="O14">
+        <v>750</v>
       </c>
     </row>
   </sheetData>
